--- a/КА_1.xlsx
+++ b/КА_1.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,12 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,65 +510,95 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SGF9_rcbf1_lvcbsup</t>
+          <t>SGF1_swctrl</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_swctrl</t>
+          <t>SGF1_cbcswi1_swctrl</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_cbcswi1_swctrl</t>
+          <t>SGF2_cbcswi1_swctrl</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_cbcswi1_swctrl</t>
+          <t>SGF1_cbcswi1_hvbctrl</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_cbcswi1_hvbctrl</t>
+          <t>SGF1_tsd</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_tsd</t>
+          <t>SGF1_xcbr1_tsd</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_xcbr1_tsd</t>
+          <t>SGF2_xcbr1_tsd</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_xcbr1_tsd</t>
+          <t>SGF3_xcbr1_tsd</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_xcbr1_tsd</t>
+          <t>SGF4_xcbr1_tsd</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_xcbr1_tsd</t>
+          <t>SGF5_xcbr1_tsd</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_xcbr1_tsd</t>
+          <t>SGF6_xcbr1_tsd</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_xcbr1_tsd</t>
+          <t>SGF1_rbrf1_tpbrf</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>SGF4_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>SGF5_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>SGF6_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SGF13_tsa</t>
         </is>
@@ -572,14 +608,14 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
+      <c r="B2" t="n">
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -599,11 +635,11 @@
       <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -611,8 +647,8 @@
       <c r="N2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>1</v>
+      <c r="O2" t="n">
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,11 +662,29 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>1</v>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -659,6 +713,9 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,7 +751,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T4_cbcswi1_swctr</t>
+          <t>T4_cbcswi1_swctrl</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -720,24 +777,39 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>T4_xcbr1_tsd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>T1_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>T1_hvcbptrc1_hvtcboff</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -746,18 +818,27 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -839,177 +920,177 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>lovn_otkl</t>
+          <t>avar_isol_V</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>urov_nasebya</t>
+          <t>niz_isol_V</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>avar_isol_V</t>
+          <t>pruzh_ne_zaved</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>niz_isol_V</t>
+          <t>Sbros</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>pruzh_ne_zaved</t>
+          <t>otkl_ot_knopk</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Sbros</t>
+          <t>oper_otkl_V</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>otkl_ot_knopk</t>
+          <t>KRV_resurs_V</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>oper_otkl_V</t>
+          <t>vnesh_blok_upr_V</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>KRV_resurs_V</t>
+          <t>kontr_emv</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>vnesh_blok_upr_V</t>
+          <t>kontr_emo1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>kontr_emv</t>
+          <t>kontr_emo2</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>kontr_emo1</t>
+          <t>rabota_emv</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>kontr_emo2</t>
+          <t>rabota_emo1</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>rabota_emv</t>
+          <t>rabota_emo2</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>rabota_emo1</t>
+          <t>OV_swctrl</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>rabota_emo2</t>
+          <t>otkl_v_ot_pu</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>OV_swctrl</t>
+          <t>otkl_v_ichm</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>otkl_v_ot_pu</t>
+          <t>mestnoe</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otkl_v_ichm</t>
+          <t>otkl_v_ot_tu</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mestnoe</t>
+          <t>otkl_v_asu</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>otkl_v_ot_tu</t>
+          <t>kluch_md_priv</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>otkl_v_asu</t>
+          <t>vkl_v_ot_pu</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>kluch_md_priv</t>
+          <t>vkl_v_ichm</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_ot_pu</t>
+          <t>distanz</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_ichm</t>
+          <t>vkl_v_ot_tu</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>distanz</t>
+          <t>vkl_v_asu</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_ot_tu</t>
+          <t>v_otkl_bk</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_asu</t>
+          <t>v_vkl_bk</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>v_otkl_bk</t>
+          <t>OV_cbcswi1_hvbctrl</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>v_vkl_bk</t>
+          <t>oper_vkl_v</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>OV_cbcswi1_hvbctrl</t>
+          <t>OV_tsd</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>oper_vkl_v</t>
+          <t>oper_otkl_v</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>OV_tsd</t>
+          <t>pusk_urov_vnesh</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>lovn_lo_otkl_avar</t>
+          <t>vnesh_otkl_zdz</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>oper_otkl_v</t>
+          <t>vnesh_otkl_urov</t>
         </is>
       </c>
     </row>
@@ -1101,17 +1182,17 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AG2" s="2" t="n">
-        <v>1</v>
+      <c r="AG2" t="n">
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -1143,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1183,6 +1264,10 @@
     <col width="20" customWidth="1" min="35" max="35"/>
     <col width="20" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1371,6 +1456,26 @@
           <t>pusk_t_lvalh</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>srab_na_sebya_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>vvod_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>otkl_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>otkl_avar_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1554,6 +1659,26 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
